--- a/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
@@ -68,9 +68,6 @@
     <t>Rating</t>
   </si>
   <si>
-    <t>TechNova Solutions</t>
-  </si>
-  <si>
     <t>www.technova.com</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>GreenField Industries</t>
-  </si>
-  <si>
     <t>www.greenfield.com</t>
   </si>
   <si>
@@ -155,9 +149,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>BlueWave Technologies</t>
-  </si>
-  <si>
     <t>www.bluewave.in</t>
   </si>
   <si>
@@ -191,9 +182,6 @@
     <t>billing@bluewave.in</t>
   </si>
   <si>
-    <t>Sunrise Healthcare</t>
-  </si>
-  <si>
     <t>www.sunrisehealth.com</t>
   </si>
   <si>
@@ -227,9 +215,6 @@
     <t>accounts@sunrisehealth.com</t>
   </si>
   <si>
-    <t>UrbanEdge Retail</t>
-  </si>
-  <si>
     <t>www.urbanedge.in</t>
   </si>
   <si>
@@ -263,9 +248,6 @@
     <t>finance@urbanedge.in</t>
   </si>
   <si>
-    <t>Apex Financial Services</t>
-  </si>
-  <si>
     <t>www.apexfinance.com</t>
   </si>
   <si>
@@ -299,9 +281,6 @@
     <t>accounts@apexfinance.com</t>
   </si>
   <si>
-    <t>CloudBridge Systems</t>
-  </si>
-  <si>
     <t>www.cloudbridge.in</t>
   </si>
   <si>
@@ -332,9 +311,6 @@
     <t>billing@cloudbridge.in</t>
   </si>
   <si>
-    <t>PrimeBuild Constructions</t>
-  </si>
-  <si>
     <t>www.primebuild.com</t>
   </si>
   <si>
@@ -368,9 +344,6 @@
     <t>accounts@primebuild.com</t>
   </si>
   <si>
-    <t>FreshMart Foods</t>
-  </si>
-  <si>
     <t>www.freshmart.in</t>
   </si>
   <si>
@@ -404,9 +377,6 @@
     <t>finance@freshmart.in</t>
   </si>
   <si>
-    <t>NovaLogix Logistics</t>
-  </si>
-  <si>
     <t>www.novalogix.com</t>
   </si>
   <si>
@@ -438,6 +408,36 @@
   </si>
   <si>
     <t>accounts@novalogix.com</t>
+  </si>
+  <si>
+    <t>TechNova Solutions_</t>
+  </si>
+  <si>
+    <t>GreenField Industries_</t>
+  </si>
+  <si>
+    <t>BlueWave Technologies_</t>
+  </si>
+  <si>
+    <t>Sunrise Healthcare_</t>
+  </si>
+  <si>
+    <t>UrbanEdge Retail_</t>
+  </si>
+  <si>
+    <t>Apex Financial Services_</t>
+  </si>
+  <si>
+    <t>CloudBridge Systems_</t>
+  </si>
+  <si>
+    <t>PrimeBuild Constructions_</t>
+  </si>
+  <si>
+    <t>FreshMart Foods_</t>
+  </si>
+  <si>
+    <t>NovaLogix Logistics_</t>
   </si>
 </sst>
 </file>
@@ -857,472 +857,472 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="N4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="N7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="N8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="N9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="N10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="146">
   <si>
     <t>Organization Name</t>
   </si>
@@ -438,6 +438,27 @@
   </si>
   <si>
     <t>NovaLogix Logistics_</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>singh</t>
+  </si>
+  <si>
+    <t>kumar</t>
+  </si>
+  <si>
+    <t>khan</t>
+  </si>
+  <si>
+    <t>yadav</t>
+  </si>
+  <si>
+    <t>sharma</t>
+  </si>
+  <si>
+    <t>verma</t>
   </si>
 </sst>
 </file>
@@ -502,13 +523,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1332,9 +1354,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="148">
   <si>
     <t>Organization Name</t>
   </si>
@@ -459,6 +459,12 @@
   </si>
   <si>
     <t>verma</t>
+  </si>
+  <si>
+    <t>maddheshiya</t>
+  </si>
+  <si>
+    <t>upadhyay</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -531,6 +537,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -940,7 +947,7 @@
       <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1354,8 +1361,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
@@ -1393,7 +1403,14 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>147</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-automation-framework-m10/src/test/resources/testScriptData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="150">
   <si>
     <t>Organization Name</t>
   </si>
@@ -465,6 +465,12 @@
   </si>
   <si>
     <t>upadhyay</t>
+  </si>
+  <si>
+    <t>vtiger429</t>
+  </si>
+  <si>
+    <t>Vtiger813</t>
   </si>
 </sst>
 </file>
@@ -818,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -1354,6 +1360,44 @@
         <v>41</v>
       </c>
     </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
